--- a/data/demo/Pulsarq-Traffic-2026-07-20~2026-07-20.xlsx
+++ b/data/demo/Pulsarq-Traffic-2026-07-20~2026-07-20.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="56">
   <si>
     <t>2026-07-20</t>
   </si>
@@ -23,19 +23,19 @@
     <t>Altavoces Inalámbricos，Mini Karaoke Portátil para Niños | Sonido Nítido Alta Fidelidad, Bocina Bluetooth 5.3 con Micrófono Inalámbrico, Diversión Musical Familiar para Fiestas y Reuniones en Casa</t>
   </si>
   <si>
-    <t>45508</t>
-  </si>
-  <si>
-    <t>37721</t>
-  </si>
-  <si>
-    <t>497</t>
-  </si>
-  <si>
-    <t>417</t>
-  </si>
-  <si>
-    <t>1.09%</t>
+    <t>69794</t>
+  </si>
+  <si>
+    <t>57171</t>
+  </si>
+  <si>
+    <t>786</t>
+  </si>
+  <si>
+    <t>654</t>
+  </si>
+  <si>
+    <t>1.13%</t>
   </si>
   <si>
     <t>604723306417839</t>
@@ -44,19 +44,40 @@
     <t>Altavoz inalámbrico portátil con Luces RGB, Radio FM y Manija - 5h Duración, TWS, TF Card, Compacto y Recargable via USB，Perfecto para viajes, fiestas y gaming</t>
   </si>
   <si>
-    <t>7177</t>
-  </si>
-  <si>
-    <t>6086</t>
-  </si>
-  <si>
-    <t>211</t>
-  </si>
-  <si>
-    <t>187</t>
-  </si>
-  <si>
-    <t>2.94%</t>
+    <t>10546</t>
+  </si>
+  <si>
+    <t>8844</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>285</t>
+  </si>
+  <si>
+    <t>3.02%</t>
+  </si>
+  <si>
+    <t>604721964231697</t>
+  </si>
+  <si>
+    <t>Bocina Radio FM/Reproductor, Compatible con Tarjeta TF, USB, Bluetooth, Aplicable para celular, computadora, Ipad y consola</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>1585</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>1.22%</t>
   </si>
   <si>
     <t>604901279130455</t>
@@ -65,70 +86,58 @@
     <t>Sopladora Turbo Inalámbrica 130000 RPM - Aire Comprimido Eléctrico con Batería 8400mAh, Carga Rápida 2.5H, Ajuste Infinito de Velocidad, Kit Limpieza Multiuso para PC, Coche, Hogar y Exteriores</t>
   </si>
   <si>
-    <t>1060</t>
-  </si>
-  <si>
-    <t>902</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>1.60%</t>
-  </si>
-  <si>
-    <t>604721964231697</t>
-  </si>
-  <si>
-    <t>Bocina Radio FM/Reproductor, Compatible con Tarjeta TF, USB, Bluetooth, Aplicable para celular, computadora, Ipad y consola</t>
-  </si>
-  <si>
-    <t>1125</t>
-  </si>
-  <si>
-    <t>1003</t>
+    <t>1614</t>
+  </si>
+  <si>
+    <t>1378</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>1.61%</t>
+  </si>
+  <si>
+    <t>604712300564882</t>
+  </si>
+  <si>
+    <t>Linkbits Altavoz Bluetooth Portátil con Stereo Inalámbrico TWS Impermeable y a Prueba de Polvo IP65 Altavoz de Graves de Rango Completo de 52mm con Doble Unidad Ligero de 215g para Camping Senderismo y Fiestas al Aire Libre</t>
+  </si>
+  <si>
+    <t>425</t>
+  </si>
+  <si>
+    <t>369</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>1.41%</t>
+  </si>
+  <si>
+    <t>604917116861510</t>
+  </si>
+  <si>
+    <t>Bocina Bluetooth Portátil Barra de Sonido, Inalámbrica con FM Radio, TWS, USB/TF, Graves Potentes para Hogar y Exteriores</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>1.07%</t>
-  </si>
-  <si>
-    <t>604712300564882</t>
-  </si>
-  <si>
-    <t>Linkbits Altavoz Bluetooth Portátil con Stereo Inalámbrico TWS Impermeable y a Prueba de Polvo IP65 Altavoz de Graves de Rango Completo de 52mm con Doble Unidad Ligero de 215g para Camping Senderismo y Fiestas al Aire Libre</t>
-  </si>
-  <si>
-    <t>293</t>
-  </si>
-  <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0.34%</t>
-  </si>
-  <si>
-    <t>604917116861510</t>
-  </si>
-  <si>
-    <t>Bocina Bluetooth Portátil Barra de Sonido, Inalámbrica con FM Radio, TWS, USB/TF, Graves Potentes para Hogar y Exteriores</t>
-  </si>
-  <si>
     <t>11</t>
   </si>
   <si>
-    <t>9.09%</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>25.00%</t>
   </si>
   <si>
     <t>604935638880082</t>
@@ -137,19 +146,19 @@
     <t>Linkbits Portable Bluetooth Speaker - 800W Peak Power, 50W Full-Range Audio with Dual Bass System &amp; Deep Bass Membranes, Powerful &amp; Distortion-Free Sound, IP65 Waterproof Dustproof, TWS Support &amp; 6H Battery for Outdoor/Party</t>
   </si>
   <si>
-    <t>834</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>5.64%</t>
+    <t>1267</t>
+  </si>
+  <si>
+    <t>959</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>5.29%</t>
   </si>
   <si>
     <t>607714432364260</t>
@@ -158,19 +167,19 @@
     <t>Portable 3-Inch Bluetooth Speaker with FM Radio, USB TF TWS, 5W Stereo Sound, Rechargeable Speaker for Home Outdoor Travel Party Camping</t>
   </si>
   <si>
-    <t>2494</t>
-  </si>
-  <si>
-    <t>2061</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>2.21%</t>
+    <t>3535</t>
+  </si>
+  <si>
+    <t>2910</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>1.87%</t>
   </si>
 </sst>
 </file>
@@ -419,10 +428,10 @@
         <v>33</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -430,25 +439,25 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -456,25 +465,25 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -482,25 +491,25 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
